--- a/Deliverables/BOM/DigiKey_BOMs/LED_Round_DigiKey.xlsx
+++ b/Deliverables/BOM/DigiKey_BOMs/LED_Round_DigiKey.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\IbrahimHyder-ReverseEngineering\Deliverables\BOM\DigiKey_BOMs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\IbrahimHyder-ReverseEngineering\Deliverables\BOM\DigiKey_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3FE38A-A5D3-4ADA-B14B-E994ABF833B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LED_Round_Board" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">LED_Round_Board!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
   <si>
     <t>Description</t>
   </si>
@@ -104,17 +105,9 @@
     <t>Quantity 5000</t>
   </si>
   <si>
-    <t xml:space="preserve">SPMWH1228FD5WARUVG
-</t>
-  </si>
-  <si>
     <t>Custom</t>
   </si>
   <si>
-    <t xml:space="preserve">LED Lighting series White, Cool 5000K 3-Step MacAdam Ellipse 2.95V 
-</t>
-  </si>
-  <si>
     <t>J2, J4</t>
   </si>
   <si>
@@ -128,10 +121,6 @@
   </si>
   <si>
     <t>LED1, LED2, LED3, LED4, LED5, LED6, LED7, LED8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor, Inc.
-</t>
   </si>
   <si>
     <t>Digikey</t>
@@ -156,10 +145,6 @@
     <t>Res 1206</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Stackpole Electronics Inc</t>
-  </si>
-  <si>
     <t>5.1R</t>
   </si>
   <si>
@@ -172,19 +157,37 @@
     <t>Connector</t>
   </si>
   <si>
-    <t>Bill of Material (BOM) for Ibrahim</t>
+    <t>HONGLITRONIC(Hongli Zhihui (HONGLITRONIC))</t>
+  </si>
+  <si>
+    <t>HL-AM-2835H421W-S1-08-HR6(SDCM&lt;6)(2800K-3100K)60mA</t>
+  </si>
+  <si>
+    <t>Local Supplier</t>
+  </si>
+  <si>
+    <t>White 2800K~3100K 2.8V~3.4V SMD,3.5x2.8x0.7mm Light Emitting Diodes (LED) RoHS</t>
+  </si>
+  <si>
+    <t>1206W4J051JT5E</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(Uniroyal Elec)</t>
+  </si>
+  <si>
+    <t>Bill of Material (BOM) for LED Round Board (Ibrahim Design)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,8 +270,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,8 +298,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -442,12 +459,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -464,21 +511,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -511,9 +549,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -539,17 +574,47 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -831,7 +896,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -845,11 +910,12 @@
     <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.140625" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
     <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -862,31 +928,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
+      <c r="A1" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
     </row>
     <row r="2" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -929,7 +995,7 @@
         <v>24</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>10</v>
@@ -959,81 +1025,81 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:40" s="11" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" s="9" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="B3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="C3" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="16">
+      <c r="F3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="13">
         <v>8</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="13">
         <f>J3*5</f>
         <v>40</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="13">
         <f>J3*1000</f>
         <v>8000</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="13">
         <f>J3*5000</f>
         <v>40000</v>
       </c>
-      <c r="N3" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="18">
-        <v>0.18</v>
-      </c>
-      <c r="P3" s="19">
+      <c r="N3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="P3" s="16">
         <f>O3*J3</f>
-        <v>1.44</v>
-      </c>
-      <c r="Q3" s="18">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="R3" s="19">
+        <v>0.8</v>
+      </c>
+      <c r="Q3" s="15">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="R3" s="16">
         <f>Q3*K3</f>
-        <v>3.84</v>
-      </c>
-      <c r="S3" s="18">
-        <v>2.6749999999999999E-2</v>
-      </c>
-      <c r="T3" s="19">
+        <v>3.8</v>
+      </c>
+      <c r="S3" s="15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="T3" s="16">
         <f>S3*L3</f>
-        <v>214</v>
-      </c>
-      <c r="U3" s="16">
-        <v>1.9769999999999999E-2</v>
-      </c>
-      <c r="V3" s="19">
+        <v>600</v>
+      </c>
+      <c r="U3" s="13">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="V3" s="16">
         <f>U3*M3</f>
-        <v>790.8</v>
-      </c>
-      <c r="W3" s="20"/>
+        <v>2440</v>
+      </c>
+      <c r="W3" s="17"/>
       <c r="X3"/>
       <c r="Y3"/>
       <c r="Z3"/>
@@ -1057,192 +1123,192 @@
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="F4" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="I4" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="26">
+      <c r="J4" s="22">
         <v>4</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="23">
         <f t="shared" ref="K4:K5" si="0">J4*5</f>
         <v>20</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="23">
         <f>J4*1000</f>
         <v>4000</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="23">
         <f>J4*5000</f>
         <v>20000</v>
       </c>
-      <c r="N4" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="29">
+      <c r="N4" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="25">
         <v>0.1</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="26">
         <f>O4*J4</f>
         <v>0.4</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="25">
         <v>0.05</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="26">
         <f>Q4*K4</f>
         <v>1</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="25">
         <v>7.9399999999999991E-3</v>
       </c>
-      <c r="T4" s="30">
+      <c r="T4" s="26">
         <f>S4*L4</f>
         <v>31.759999999999998</v>
       </c>
-      <c r="U4" s="31">
+      <c r="U4" s="27">
         <v>6.5599999999999999E-3</v>
       </c>
-      <c r="V4" s="32">
+      <c r="V4" s="28">
         <f>U4*M4</f>
         <v>131.19999999999999</v>
       </c>
-      <c r="W4" s="33"/>
+      <c r="W4" s="29"/>
     </row>
     <row r="5" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34">
+      <c r="A5" s="30">
         <f>A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="15" t="s">
+      <c r="D5" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="16">
+      <c r="H5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="39">
         <v>2</v>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="40">
         <f>J5*1000</f>
         <v>2000</v>
       </c>
-      <c r="M5" s="35">
+      <c r="M5" s="40">
         <f>J5*5000</f>
         <v>10000</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="T5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="U5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="V5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="W5" s="36" t="s">
-        <v>31</v>
+      <c r="N5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="U5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="V5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="W5" s="31" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
       <c r="R6" s="3">
         <f>SUM(R3:R4)</f>
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="3">
         <f>SUM(T3:T4)</f>
-        <v>245.76</v>
+        <v>631.76</v>
       </c>
       <c r="V6" s="7">
         <f>SUM(V3:V4)</f>
-        <v>922</v>
+        <v>2571.1999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:40" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33"/>
       <c r="P7" s="2">
         <f>SUM(P3:P4)</f>
-        <v>1.8399999999999999</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="R7" s="4">
         <f>R6/5</f>
-        <v>0.96799999999999997</v>
+        <v>0.96</v>
       </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
@@ -1333,12 +1399,11 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N3" r:id="rId1"/>
-    <hyperlink ref="N4" r:id="rId2"/>
+    <hyperlink ref="N4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup scale="39" orientation="landscape" blackAndWhite="1" r:id="rId3"/>
+  <pageSetup scale="39" orientation="landscape" blackAndWhite="1" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
